--- a/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:26:45+00:00</t>
+    <t>2026-09-09T12:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:40:12+00:00</t>
+    <t>2026-09-09T12:51:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:51:05+00:00</t>
+    <t>2026-09-09T12:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:56:34+00:00</t>
+    <t>2026-09-09T13:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:08:30+00:00</t>
+    <t>2026-09-09T13:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:18:24+00:00</t>
+    <t>2026-09-09T13:33:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:33:26+00:00</t>
+    <t>2026-09-09T13:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3010" uniqueCount="334">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:48:19+00:00</t>
+    <t>2026-09-11T10:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -465,6 +465,12 @@
   </si>
   <si>
     <t>Specimen.extension[anzahlAliquots]</t>
+  </si>
+  <si>
+    <t>Biobank.Bioprobe.Infektiositaets-Status</t>
+  </si>
+  <si>
+    <t>Markiert eine Probe als (potentiell) infektiös.</t>
   </si>
   <si>
     <t>Biobank.Bioprobe.Container</t>
@@ -1329,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK91"/>
+  <dimension ref="A1:AK92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="50.109375" customWidth="true" bestFit="true"/>
@@ -3270,7 +3276,7 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>146</v>
@@ -3339,18 +3345,18 @@
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>147</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3373,13 +3379,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3430,7 +3436,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3442,29 +3448,29 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -3476,17 +3482,15 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3523,31 +3527,31 @@
         <v>73</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>73</v>
@@ -3555,14 +3559,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3575,26 +3579,24 @@
         <v>73</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O22" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
       </c>
@@ -3630,19 +3632,19 @@
         <v>73</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3662,42 +3664,46 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>152</v>
+        <v>106</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>73</v>
       </c>
@@ -3745,30 +3751,30 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3791,13 +3797,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3848,7 +3854,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3863,15 +3869,15 @@
         <v>73</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3894,13 +3900,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3951,7 +3957,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3966,15 +3972,15 @@
         <v>73</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3985,7 +3991,7 @@
         <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>73</v>
@@ -3997,13 +4003,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4054,13 +4060,13 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>73</v>
@@ -4069,7 +4075,7 @@
         <v>73</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27">
@@ -4088,7 +4094,7 @@
         <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -4100,7 +4106,7 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>164</v>
@@ -4163,24 +4169,24 @@
         <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4203,13 +4209,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4260,7 +4266,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4272,29 +4278,29 @@
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -4306,17 +4312,15 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>73</v>
@@ -4353,31 +4357,31 @@
         <v>73</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>73</v>
@@ -4385,14 +4389,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4405,26 +4409,24 @@
         <v>73</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O30" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>73</v>
       </c>
@@ -4460,19 +4462,19 @@
         <v>73</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4492,42 +4494,46 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>73</v>
       </c>
@@ -4575,30 +4581,30 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>171</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4621,13 +4627,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4678,7 +4684,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4693,15 +4699,15 @@
         <v>73</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4724,13 +4730,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4781,7 +4787,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4796,15 +4802,15 @@
         <v>73</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4827,13 +4833,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4884,7 +4890,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4899,15 +4905,15 @@
         <v>73</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4933,10 +4939,10 @@
         <v>115</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4987,7 +4993,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5002,15 +5008,15 @@
         <v>73</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5033,13 +5039,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5090,7 +5096,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5105,15 +5111,15 @@
         <v>73</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5136,13 +5142,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5193,7 +5199,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5205,18 +5211,18 @@
         <v>73</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5239,13 +5245,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>83</v>
+        <v>191</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5296,7 +5302,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5308,29 +5314,29 @@
         <v>73</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>73</v>
@@ -5342,17 +5348,15 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>73</v>
@@ -5389,31 +5393,31 @@
         <v>73</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>73</v>
@@ -5421,14 +5425,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5441,26 +5445,24 @@
         <v>73</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O40" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>73</v>
       </c>
@@ -5496,19 +5498,19 @@
         <v>73</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -5528,42 +5530,46 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>173</v>
+        <v>88</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>195</v>
+        <v>106</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>73</v>
       </c>
@@ -5611,30 +5617,30 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>194</v>
+        <v>109</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>196</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5657,13 +5663,13 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5714,7 +5720,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5729,15 +5735,15 @@
         <v>73</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5760,13 +5766,13 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5817,7 +5823,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -5863,13 +5869,13 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>203</v>
+        <v>98</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5935,15 +5941,15 @@
         <v>73</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5966,13 +5972,13 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6023,7 +6029,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6038,7 +6044,7 @@
         <v>73</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46">
@@ -6069,13 +6075,13 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6141,7 +6147,7 @@
         <v>73</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47">
@@ -6160,7 +6166,7 @@
         <v>74</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>73</v>
@@ -6172,13 +6178,13 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6235,7 +6241,7 @@
         <v>74</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>73</v>
@@ -6244,7 +6250,7 @@
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="48">
@@ -6263,7 +6269,7 @@
         <v>74</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>73</v>
@@ -6275,7 +6281,7 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>213</v>
@@ -6338,24 +6344,24 @@
         <v>74</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6378,13 +6384,13 @@
         <v>73</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6435,7 +6441,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>85</v>
+        <v>214</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6447,29 +6453,29 @@
         <v>73</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>73</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>73</v>
@@ -6481,17 +6487,15 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>73</v>
@@ -6528,31 +6532,31 @@
         <v>73</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>73</v>
@@ -6560,14 +6564,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -6580,26 +6584,24 @@
         <v>73</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O51" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>73</v>
       </c>
@@ -6635,19 +6637,19 @@
         <v>73</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -6667,42 +6669,46 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>173</v>
+        <v>88</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>219</v>
+        <v>106</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>73</v>
       </c>
@@ -6750,30 +6756,30 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>220</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6796,13 +6802,13 @@
         <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6853,7 +6859,7 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -6868,15 +6874,15 @@
         <v>73</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6899,13 +6905,13 @@
         <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6956,7 +6962,7 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
@@ -6971,15 +6977,15 @@
         <v>73</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7002,13 +7008,13 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>132</v>
+        <v>205</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7059,7 +7065,7 @@
         <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7074,7 +7080,7 @@
         <v>73</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>73</v>
+        <v>228</v>
       </c>
     </row>
     <row r="56">
@@ -7185,7 +7191,7 @@
         <v>231</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7208,13 +7214,13 @@
         <v>73</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7265,7 +7271,7 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -7277,18 +7283,18 @@
         <v>73</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7311,13 +7317,13 @@
         <v>73</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>83</v>
+        <v>235</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>84</v>
+        <v>235</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7368,7 +7374,7 @@
         <v>73</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>85</v>
+        <v>234</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -7380,10 +7386,10 @@
         <v>73</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>73</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
@@ -7395,14 +7401,14 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>73</v>
@@ -7414,17 +7420,15 @@
         <v>73</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>73</v>
@@ -7461,31 +7465,31 @@
         <v>73</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>73</v>
@@ -7500,7 +7504,7 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -7513,26 +7517,24 @@
         <v>73</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O60" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>73</v>
       </c>
@@ -7568,19 +7570,19 @@
         <v>73</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -7607,7 +7609,7 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -7620,22 +7622,26 @@
         <v>73</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>242</v>
+        <v>106</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>73</v>
       </c>
@@ -7683,7 +7689,7 @@
         <v>73</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>241</v>
+        <v>109</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
@@ -7695,18 +7701,18 @@
         <v>73</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>243</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7717,7 +7723,7 @@
         <v>74</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>73</v>
@@ -7729,13 +7735,13 @@
         <v>73</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7786,30 +7792,30 @@
         <v>73</v>
       </c>
       <c r="AF62" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK62" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7835,10 +7841,10 @@
         <v>115</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7889,30 +7895,30 @@
         <v>73</v>
       </c>
       <c r="AF63" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK63" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7923,7 +7929,7 @@
         <v>74</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>73</v>
@@ -7935,13 +7941,13 @@
         <v>73</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7992,30 +7998,30 @@
         <v>73</v>
       </c>
       <c r="AF64" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK64" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>255</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8026,7 +8032,7 @@
         <v>74</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>73</v>
@@ -8038,13 +8044,13 @@
         <v>73</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8095,30 +8101,30 @@
         <v>73</v>
       </c>
       <c r="AF65" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK65" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>259</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8144,10 +8150,10 @@
         <v>115</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8198,30 +8204,30 @@
         <v>73</v>
       </c>
       <c r="AF66" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK66" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8244,13 +8250,13 @@
         <v>73</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8301,30 +8307,30 @@
         <v>73</v>
       </c>
       <c r="AF67" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK67" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8335,7 +8341,7 @@
         <v>74</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>73</v>
@@ -8347,13 +8353,13 @@
         <v>73</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8404,30 +8410,30 @@
         <v>73</v>
       </c>
       <c r="AF68" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK68" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8453,10 +8459,10 @@
         <v>115</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8507,7 +8513,7 @@
         <v>73</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
@@ -8522,15 +8528,15 @@
         <v>73</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8541,7 +8547,7 @@
         <v>74</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>73</v>
@@ -8553,13 +8559,13 @@
         <v>73</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8610,30 +8616,30 @@
         <v>73</v>
       </c>
       <c r="AF70" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK70" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>279</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8644,7 +8650,7 @@
         <v>74</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>73</v>
@@ -8656,13 +8662,13 @@
         <v>73</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8713,30 +8719,30 @@
         <v>73</v>
       </c>
       <c r="AF71" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK71" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8747,7 +8753,7 @@
         <v>74</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>73</v>
@@ -8759,13 +8765,13 @@
         <v>73</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8816,22 +8822,22 @@
         <v>73</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>72</v>
+        <v>285</v>
       </c>
     </row>
     <row r="73">
@@ -8862,13 +8868,13 @@
         <v>73</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8919,7 +8925,7 @@
         <v>73</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>85</v>
+        <v>286</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
@@ -8931,29 +8937,29 @@
         <v>73</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>73</v>
@@ -8965,17 +8971,15 @@
         <v>73</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>73</v>
@@ -9012,31 +9016,31 @@
         <v>73</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>73</v>
@@ -9044,14 +9048,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9064,26 +9068,24 @@
         <v>73</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O75" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>73</v>
       </c>
@@ -9119,19 +9121,19 @@
         <v>73</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
@@ -9151,14 +9153,14 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -9171,22 +9173,26 @@
         <v>73</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>290</v>
+        <v>106</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>73</v>
       </c>
@@ -9234,7 +9240,7 @@
         <v>73</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>289</v>
+        <v>109</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
@@ -9246,18 +9252,18 @@
         <v>73</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>291</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9268,7 +9274,7 @@
         <v>74</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>73</v>
@@ -9280,13 +9286,13 @@
         <v>73</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9337,41 +9343,41 @@
         <v>73</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>85</v>
+        <v>291</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>73</v>
+        <v>293</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>73</v>
@@ -9383,17 +9389,15 @@
         <v>73</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>73</v>
@@ -9430,31 +9434,31 @@
         <v>73</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>73</v>
@@ -9462,14 +9466,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -9482,26 +9486,24 @@
         <v>73</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O79" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>73</v>
       </c>
@@ -9537,19 +9539,19 @@
         <v>73</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>74</v>
@@ -9569,42 +9571,46 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>296</v>
+        <v>106</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>73</v>
       </c>
@@ -9652,30 +9658,30 @@
         <v>73</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>295</v>
+        <v>109</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>297</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9701,10 +9707,10 @@
         <v>82</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9755,7 +9761,7 @@
         <v>73</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
@@ -9770,15 +9776,15 @@
         <v>73</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9804,10 +9810,10 @@
         <v>82</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9858,7 +9864,7 @@
         <v>73</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>74</v>
@@ -9873,15 +9879,15 @@
         <v>73</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9904,13 +9910,13 @@
         <v>73</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9961,7 +9967,7 @@
         <v>73</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
@@ -9976,15 +9982,15 @@
         <v>73</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10007,13 +10013,13 @@
         <v>73</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>308</v>
+        <v>115</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10064,7 +10070,7 @@
         <v>73</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
@@ -10079,15 +10085,15 @@
         <v>73</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10110,13 +10116,13 @@
         <v>73</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>111</v>
+        <v>310</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10167,7 +10173,7 @@
         <v>73</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
@@ -10182,15 +10188,15 @@
         <v>73</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10216,10 +10222,10 @@
         <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10270,7 +10276,7 @@
         <v>73</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -10285,15 +10291,15 @@
         <v>73</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10316,13 +10322,13 @@
         <v>73</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10373,7 +10379,7 @@
         <v>73</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -10388,15 +10394,15 @@
         <v>73</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10422,10 +10428,10 @@
         <v>82</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10476,7 +10482,7 @@
         <v>73</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>74</v>
@@ -10491,15 +10497,15 @@
         <v>73</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10525,10 +10531,10 @@
         <v>82</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10579,7 +10585,7 @@
         <v>73</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
@@ -10594,15 +10600,15 @@
         <v>73</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10625,13 +10631,13 @@
         <v>73</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10682,7 +10688,7 @@
         <v>73</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>74</v>
@@ -10697,15 +10703,15 @@
         <v>73</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10716,7 +10722,7 @@
         <v>74</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>73</v>
@@ -10728,13 +10734,13 @@
         <v>73</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10785,22 +10791,125 @@
         <v>73</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G92" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AI91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK91" t="s" s="2">
+      <c r="H92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>331</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-Biobank.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:07:49+00:00</t>
+    <t>2026-09-11T10:33:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
